--- a/output/graficos_nacionales/plot_nacional_edad_e_rezjov_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_edad_e_rezjov_a_2018.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:20</t>
+    <t xml:space="preserve">2026-10-01 23:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_edad_e_rezjov_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_edad_e_rezjov_a_2018.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:08</t>
+    <t xml:space="preserve">2026-10-05 06:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
